--- a/VALUO/pozemky_data.xlsx
+++ b/VALUO/pozemky_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,17 +530,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V-31029/2025-101</t>
+          <t>V-46914/2025-101</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45796.46834490741</v>
+        <v>45861.48016203703</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>3071</v>
+        <v>103</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -560,17 +560,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,26 +579,26 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24500000</v>
+        <v>2222225</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>manipulační plocha</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1433/12, 1433/13</t>
+          <t>1492/21</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>21575</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V-25140/2025-101</t>
+          <t>V-41203/2025-101</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45770.33414351852</v>
+        <v>45838.34513888889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>43241</v>
+        <v>9219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -638,17 +638,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -657,26 +657,26 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>100000000</v>
+        <v>129900000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>IZ, PS, ZMK</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>jiná plocha, orná půda, ovocný sad</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1480/3, 1480/4, 1481/1, 2352/1, 2352/10, 2352/11, 2352/12, 2352/2, 2352/20, 2352/22, 2352/30, 2352/31, 2352/4</t>
+          <t>439/2</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>14090</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V-19568/2025-101</t>
+          <t>V-35550/2025-101</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2025</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45744.49373842592</v>
+        <v>45813.40625</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>9833</v>
+        <v>374</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -716,17 +716,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -735,26 +735,26 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>54000000</v>
+        <v>10000000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>DH, IZ</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>orná půda, zastavěná plocha a nádvoří</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2372/31, 2372/34, 2372/35, 2372/36, 2372/87</t>
+          <t>121/4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>26738</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V-9542/2025-101</t>
+          <t>V-32934/2025-101</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45702.36376157407</v>
+        <v>45804.41574074074</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>1022</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -794,17 +794,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1000</v>
+        <v>12247107</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>OB, ZMK</t>
+          <t>SV-D</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>11/2, 11/3, 521/2, 521/3</t>
+          <t>1653/3</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11983</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V-77826/2024-101</t>
+          <t>V-5743/2025-101</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45649.40625</v>
+        <v>45686.46331018519</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>10046</v>
+        <v>515</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -872,17 +872,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732451</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -891,26 +891,26 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>29900000</v>
+        <v>11858000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>DH, ZMK</t>
+          <t>SV-D</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>jiná plocha, koryto vodního toku přirozené nebo upravené, orná půda</t>
+          <t>jiná plocha, zeleň</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2370/75, 2370/76, 2477/3, 844/12</t>
+          <t>890/7, 906/17, 908/8</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>23025</t>
         </is>
       </c>
     </row>
@@ -920,28 +920,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V-76318/2024-101</t>
+          <t>V-5110/2025-101</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2025</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45644.39130787037</v>
+        <v>45684.48190972222</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zřízení zástavního práva podle obč.z.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>41858</v>
+        <v>522</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -950,17 +950,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -969,26 +969,26 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>54298200</v>
+        <v>6680000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>IZ, NL/SP, OV, PS/SP, ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda, ostatní komunikace</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1470/176, 1477/4, 1478/11, 2350/4, 2350/5, 2350/6, 2350/7, 2351/1, 2351/3, 2351/6, 2352/21, 2352/33, 2352/34, 2352/5, 2444</t>
+          <t>439/52</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>12797</t>
         </is>
       </c>
     </row>
@@ -998,17 +998,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V-11102/2024-210</t>
+          <t>V-3594/2025-101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45595.50548611111</v>
+        <v>45677.5709375</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>14786</v>
+        <v>1201</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>793213</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Hodkovice u Zlatníků</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1047,26 +1047,26 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>185480</v>
+        <v>52000000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>NL, OB, ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda, trvalý travní porost, zahrada</t>
+          <t>zeleň</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>269/2, 269/4, 507/4, 991/9, 992/8, 993/7</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>43297</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V-60292/2024-101</t>
+          <t>V-76826/2024-101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>45581.40625</v>
+        <v>45644.67494212963</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3681</v>
+        <v>2723</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1125,26 +1125,26 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>8950000</v>
+        <v>30000000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>DH, ZMK</t>
+          <t>OB, SV</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha, zahrada</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1015/53, 835/203</t>
+          <t>2285/1, 2286</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>11017</t>
         </is>
       </c>
     </row>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V-57996/2024-101</t>
+          <t>V-75618/2024-101</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45569.49055555555</v>
+        <v>45642.52130787037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>11516</v>
+        <v>196</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1203,26 +1203,26 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>17484875</v>
+        <v>6700000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ZMK, ZMK/SV-B</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2375/6, 2375/7</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>34184</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V-55801/2024-101</t>
+          <t>V-75458/2024-101</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>45560.66366898148</v>
+        <v>45642.39537037037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>21915</v>
+        <v>15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1262,17 +1262,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1281,26 +1281,26 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>18750000</v>
+        <v>380000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>NL, ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>orná půda, ostatní komunikace</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>933/2, 933/3, 934/28, 934/29</t>
+          <t>3496/9</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>25333</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V-42960/2024-101</t>
+          <t>V-75303/2024-101</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45497.68697916667</v>
+        <v>45639.48475694445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1005</v>
+        <v>2872</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1340,17 +1340,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1359,26 +1359,26 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>750000</v>
+        <v>54955500</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>VN-F</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>980/7</t>
+          <t>1676/65</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>19135</t>
         </is>
       </c>
     </row>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-40708/2024-101</t>
+          <t>V-75240/2024-101</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45485.40625</v>
+        <v>45639.45305555555</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>515</v>
+        <v>36</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1437,26 +1437,26 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>900</v>
+        <v>601612</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2373/33</t>
+          <t>21/11, 21/12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16711</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V-38354/2024-101</t>
+          <t>V-69272/2024-101</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2024</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45474.40625</v>
+        <v>45617.5034375</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>515</v>
+        <v>994</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1496,17 +1496,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1515,26 +1515,26 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>900</v>
+        <v>28000000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB, OV</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zeleň</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2373/33</t>
+          <t>2845/14, 2855/8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28169</t>
         </is>
       </c>
     </row>
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-32511/2024-101</t>
+          <t>V-67618/2024-101</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2024</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45448.40625</v>
+        <v>45610.56474537037</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>152</v>
+        <v>1123</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1574,17 +1574,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732583</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Horní Měcholupy</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1593,26 +1593,26 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3168</v>
+        <v>12000000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OV-F, SP</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>lesní pozemek</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1187/2</t>
+          <t>2747/73, 520/17, 520/48, 520/52</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10686</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V-32174/2024-101</t>
+          <t>V-65779/2024-101</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2024</v>
       </c>
       <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45603.57430555556</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>45447.36206018519</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" t="n">
-        <v>6461</v>
+        <v>3210</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1652,17 +1652,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732583</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Horní Měcholupy</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1671,26 +1671,26 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>50000000</v>
+        <v>34409856</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OB-B, ZMK</t>
+          <t>OV-E, OV-F, SP</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha, zeleň</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2349/15, 2349/47</t>
+          <t>2747/71, 2747/72, 2747/73, 518/38, 520/20, 520/49, 520/51, 521/381, 521/415, 521/416</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>10720</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V-31283/2024-101</t>
+          <t>V-40630/2024-101</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2024</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45442.40625</v>
+        <v>45485.38900462963</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>515</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1749,26 +1749,26 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>50000</v>
+        <v>175000</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>PZO</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zastavěná plocha a nádvoří</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2373/33</t>
+          <t>4031/31</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>35000</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V-24135/2024-101</t>
+          <t>V-36255/2024-101</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2024</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45407.52950231481</v>
+        <v>45464.46828703704</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>117764</v>
+        <v>21</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1808,17 +1808,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1827,26 +1827,26 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>13000000</v>
+        <v>300000</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>LR, NL, NL/SV-C, OB, OP, OP/OB-B, OP/ZMK, VN, VOP, ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>jiná plocha, koryto vodního toku přirozené nebo upravené, orná půda, ostatní komunikace, sportoviště a rekreační plocha, trvalý travní porost</t>
+          <t>zastavěná plocha a nádvoří</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1004/4, 1005/4, 1006/8, 13/2, 522/1, 526/8, 529/7, 670/2, 670/3, 835/11, 836/9, 845/24, 845/25, 846/2, 875/15, 875/16, 875/17, 876/3, 876/5, 878/14, 878/15, 922/13, 972/2, 973/2, 984/3, 985/7, 987/14, 987/15, 990/2, 991/2</t>
+          <t>654/7</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14286</t>
         </is>
       </c>
     </row>
@@ -1856,28 +1856,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V-23453/2024-101</t>
+          <t>V-35213/2024-101</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2024</v>
       </c>
       <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45461.3869212963</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>45405.48844907407</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" t="n">
-        <v>4140</v>
+        <v>433</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1905,26 +1905,26 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>800000</v>
+        <v>5500000</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV-D</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha, zahrada</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2373/23</t>
+          <t>4174/1, 4174/2, 4174/3, 4174/4, 4174/5</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>12702</t>
         </is>
       </c>
     </row>
@@ -1934,17 +1934,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>V-21507/2024-101</t>
+          <t>V-27182/2024-101</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2024</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45397.52927083334</v>
+        <v>45425.49413194445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>515</v>
+        <v>17</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1992,17 +1992,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2373/33</t>
+          <t>4501/152</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11765</t>
         </is>
       </c>
     </row>
@@ -2012,17 +2012,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V-717/2024-101</t>
+          <t>V-26380/2024-101</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2024</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45296.44802083333</v>
+        <v>45419.41424768518</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>583</v>
+        <v>1092</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732451</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2061,26 +2061,26 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>100000</v>
+        <v>25300000</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OP, SV-D</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1867/13</t>
+          <t>890/68, 906/15, 906/16, 908/6, 943/2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>23168</t>
         </is>
       </c>
     </row>
@@ -2090,28 +2090,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V-345/2024-101</t>
+          <t>V-9328/2024-101</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2024</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45294.63649305556</v>
+        <v>45338.38943287037</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zániku předkupního práva</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>986</v>
+        <v>16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2120,17 +2120,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732451</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2139,26 +2139,26 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>8929970</v>
+        <v>176000</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>OB-C, OB-D, ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>jiná plocha, ostatní komunikace</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2420/4, 2420/5, 2420/6, 816/21, 824/28, 825/1, 825/12, 826/4</t>
+          <t>498/4</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>11000</t>
         </is>
       </c>
     </row>
@@ -2168,17 +2168,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>V-68131/2023-101</t>
+          <t>V-4195/2024-101</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2024</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45278.44791666666</v>
+        <v>45315.37703703704</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2217,26 +2217,26 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5227</v>
+        <v>254037</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>trvalý travní porost</t>
+          <t>zastavěná plocha a nádvoří</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>135/6</t>
+          <t>654/7</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>12097</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2246,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V-48074/2023-101</t>
+          <t>V-70691/2023-101</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45181.44802083333</v>
+        <v>45289.48384259259</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>515</v>
+        <v>309</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2295,26 +2295,26 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>500</v>
+        <v>6675000</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2373/33</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21602</t>
         </is>
       </c>
     </row>
@@ -2324,17 +2324,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>V-47590/2023-101</t>
+          <t>V-70042/2023-101</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45177.4828587963</v>
+        <v>45282.50065972222</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>41</v>
+        <v>316</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732451</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2373,26 +2373,26 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>115000</v>
+        <v>10000000</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>trvalý travní porost</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2110/38</t>
+          <t>80/2</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>31646</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>V-42230/2023-101</t>
+          <t>V-64568/2023-101</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2023</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45147.62395833333</v>
+        <v>45260.45768518518</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>6210</v>
+        <v>1022</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2451,26 +2451,26 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>43000000</v>
+        <v>12775000</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV-D</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>manipulační plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1433/10, 1433/11, 1433/12, 1433/13</t>
+          <t>1653/3</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
@@ -2480,17 +2480,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>V-37658/2023-101</t>
+          <t>V-46411/2022-101</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45124.44854166666</v>
+        <v>44775.4552662037</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4540</v>
+        <v>302</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2510,17 +2510,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2529,26 +2529,26 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>800000</v>
+        <v>13500000</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2350/9, 2352/28, 2352/32</t>
+          <t>524/15</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>44702</t>
         </is>
       </c>
     </row>
@@ -2558,17 +2558,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>V-36815/2023-101</t>
+          <t>V-45270/2022-101</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45118.99244212963</v>
+        <v>44769.5263425926</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>2104</v>
+        <v>558</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2607,26 +2607,26 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>5700000</v>
+        <v>9000000</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV-D</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>jiná plocha, zahrada</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1158, 1159</t>
+          <t>1302/48</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>16129</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2636,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V-7793/2023-101</t>
+          <t>V-43470/2022-101</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>44970.34607638889</v>
+        <v>44761.47697916667</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>4130</v>
+        <v>226</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>18174800</v>
+        <v>5000000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>DH, ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>manipulační plocha, ostatní komunikace, silnice</t>
+          <t>zahrada, zastavěná plocha a nádvoří</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>879/16, 879/17, 879/4, 880/17</t>
+          <t>386/1, 386/2</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>22124</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>V-39047/2022-101</t>
+          <t>V-27575/2022-101</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2022</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>44735.54371527778</v>
+        <v>44683.70978009259</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>14842</v>
+        <v>210</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2744,17 +2744,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732052</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Hostivař</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2763,26 +2763,26 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>30400000</v>
+        <v>3500000</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PS, SV-C, ZMK</t>
+          <t>OV-C</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>jiná plocha, orná půda, ovocný sad</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1871, 1872, 2366/34</t>
+          <t>522/4</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>16667</t>
         </is>
       </c>
     </row>
@@ -2792,17 +2792,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>V-20265/2022-101</t>
+          <t>V-66483/2020-101</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44649.48006944444</v>
+        <v>44141.43905092592</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>99</v>
+        <v>910</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2822,17 +2822,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2841,26 +2841,26 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>50000</v>
+        <v>12500000</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB-D</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2356/111</t>
+          <t>349/227</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>13736</t>
         </is>
       </c>
     </row>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V-4695/2022-101</t>
+          <t>V-21491/2020-101</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44582.50694444445</v>
+        <v>43941.4478125</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>781</v>
+        <v>522</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2919,26 +2919,26 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>63261</v>
+        <v>6680000</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>koryto vodního toku přirozené nebo upravené, trvalý travní porost</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>991/7, 992/6, 993/5</t>
+          <t>439/52</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>12797</t>
         </is>
       </c>
     </row>
@@ -2948,17 +2948,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>V-4586/2022-101</t>
+          <t>V-15586/2020-101</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44582.4278125</v>
+        <v>43902.48244212963</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>4128</v>
+        <v>832</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2978,17 +2978,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2997,11 +2997,11 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>16512000</v>
+        <v>9000000</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>OB-D</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>844/8</t>
+          <t>349/25</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>10817</t>
         </is>
       </c>
     </row>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>V-97143/2021-101</t>
+          <t>V-86046/2019-101</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44553.41902777777</v>
+        <v>43829.60714120371</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>4128</v>
+        <v>308</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Štěrboholy</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3075,26 +3075,26 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2752000</v>
+        <v>4250000</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>844/8</t>
+          <t>269, 270</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>13799</t>
         </is>
       </c>
     </row>
@@ -3104,17 +3104,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V-97142/2021-101</t>
+          <t>V-86597/2014-101</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44553.41819444444</v>
+        <v>41996.50581018518</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>4128</v>
+        <v>838</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3134,17 +3134,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Malešice</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>720984</t>
+          <t>731943</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Písnice</t>
+          <t>Strašnice</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2064000</v>
+        <v>15000000</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>VV</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3167,1338 +3167,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>844/8</t>
+          <t>1590/14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>V-97140/2021-101</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>44553.41729166666</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4128</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>720984</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>2752000</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>844/8</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>V-97139/2021-101</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>44553.4165625</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4128</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>720984</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>1032000</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>844/8</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>V-91526/2021-101</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D38" t="n">
-        <v>12</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>44536.49143518518</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4128</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>720984</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>2752000</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>844/8</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>V-90297/2021-101</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D39" t="n">
-        <v>12</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>44531.47324074074</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>6874</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>34356252</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>orná půda</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2372/5, 2372/88</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>V-89035/2021-101</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D40" t="n">
-        <v>12</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>44526.36560185185</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2245</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2368/16, 2368/30, 2477/7</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>3786</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>V-56400/2021-101</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>44399.5066087963</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>14842</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>PS, SV-C, ZMK</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>jiná plocha, orná půda, ovocný sad</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1871, 1872, 2366/34</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2358</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>V-54735/2021-101</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>44393.43516203704</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2696</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>428664</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2339/118, 2340/3</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>V-51944/2021-101</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>44379.52472222222</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>6354</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>11063400</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>OB-C, ZMK</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>jiná plocha, lesní pozemek</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2339/126, 2339/2, 2340/2</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>V-33534/2021-101</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D44" t="n">
-        <v>6</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>44320.56076388889</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Smlouva kupní, Smlouva o zřízení věcného břemene - bezúplatná</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2702</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>OB-C, ZMK</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>orná půda, ostatní komunikace</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2356/179, 2356/212, 2356/219</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>4441</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>V-22856/2021-101</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>44280.55900462963</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>825</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>720984</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Písnice</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>manipulační plocha</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>880/15</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>3394</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>V-18487/2021-101</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>44266.38175925926</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>417</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>75000</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1190/5, 1190/6</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>V-5383/2021-101</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>44221.42939814815</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>12364</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>240000</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>LR, VOP, ZMK</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>lesní pozemek, neplodná půda, trvalý travní porost</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1868/1, 2361/21, 2361/27, 2361/43, 2522/20</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>V-61549/2020-101</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D48" t="n">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>44123.40917824074</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" t="n">
-        <v>16282</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>PS, ZMK</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>orná půda, ovocný sad</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2352/10, 2352/12, 2352/2, 2352/4</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>V-28713/2020-101</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D49" t="n">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>43976.38417824074</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>4</v>
-      </c>
-      <c r="H49" t="n">
-        <v>7403</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>24800050</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>DH, IZ, ZMK</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>orná půda</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>2370/28, 2370/41, 2370/42, 2370/47</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>3350</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>V-24337/2020-101</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D50" t="n">
-        <v>5</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>43955.53079861111</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2245</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>2368/16, 2368/2, 2477/7</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>3341</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>V-18592/2020-101</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>43921.42497685185</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>10</v>
-      </c>
-      <c r="H51" t="n">
-        <v>8112</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>6250000</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>OV-C, ZMK</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>jiná plocha, zeleň</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>2339/113, 2339/120, 2339/122, 2339/136, 2339/137, 2339/139, 2339/140, 2339/145, 2339/147, 2339/68</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>V-85048/2019-101</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>43822.54815972222</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1602</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>3204000</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>orná půda</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2353/15</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2000</t>
+          <t>17900</t>
         </is>
       </c>
     </row>

--- a/VALUO/pozemky_data.xlsx
+++ b/VALUO/pozemky_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,17 +530,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V-46914/2025-101</t>
+          <t>V-4756/2025-509</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45861.48016203703</v>
+        <v>45897.49290509259</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -551,26 +551,26 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>103</v>
+        <v>1250</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,26 +579,22 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2222225</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>2990000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1492/21</t>
+          <t>280/49</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>2392</t>
         </is>
       </c>
     </row>
@@ -608,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V-41203/2025-101</t>
+          <t>V-3692/2025-509</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -618,7 +614,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45838.34513888889</v>
+        <v>45840.56797453704</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -629,26 +625,26 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9219</v>
+        <v>2174</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633461</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -657,26 +653,22 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>129900000</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OB-C</t>
-        </is>
-      </c>
+        <v>424080</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>ostatní komunikace</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>439/2</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -686,7 +678,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V-35550/2025-101</t>
+          <t>V-3541/2025-509</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -696,7 +688,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45813.40625</v>
+        <v>45833.40972222222</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -704,29 +696,29 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>374</v>
+        <v>2010</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633461</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -735,26 +727,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>121/4</t>
+          <t>525/1, 525/26</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -764,17 +752,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V-32934/2025-101</t>
+          <t>V-3204/2025-509</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45804.41574074074</v>
+        <v>45818.52278935185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -782,29 +770,29 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1022</v>
+        <v>5482</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633411</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -813,26 +801,22 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12247107</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>SV-D</t>
-        </is>
-      </c>
+        <v>6800000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda, trvalý travní porost</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1653/3</t>
+          <t>385, 386, 413</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>1240</t>
         </is>
       </c>
     </row>
@@ -842,17 +826,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V-5743/2025-101</t>
+          <t>V-2908/2025-509</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45686.46331018519</v>
+        <v>45804.55275462963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -860,29 +844,29 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>515</v>
+        <v>769</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>732451</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -891,26 +875,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11858000</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>SV-D</t>
-        </is>
-      </c>
+        <v>1900000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>jiná plocha, zeleň</t>
+          <t>manipulační plocha</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>890/7, 906/17, 908/8</t>
+          <t>458/20</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>2471</t>
         </is>
       </c>
     </row>
@@ -920,47 +900,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V-5110/2025-101</t>
+          <t>V-2833/2025-509</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2025</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45684.48190972222</v>
+        <v>45801.37851851852</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smlouva kupní, Smlouva o zřízení zástavního práva podle obč.z.</t>
+          <t>Smlouva kupní</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>522</v>
+        <v>441</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633461</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -969,26 +949,22 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6680000</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>439/52</t>
+          <t>125/1, 125/2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>2268</t>
         </is>
       </c>
     </row>
@@ -998,17 +974,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V-3594/2025-101</t>
+          <t>V-2498/2025-509</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2025</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45677.5709375</v>
+        <v>45786.38336805555</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1016,29 +992,29 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>1201</v>
+        <v>17922</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí u Teplic</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633381</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1047,26 +1023,22 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>4000000</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>zeleň</t>
+          <t>manipulační plocha, neplodná půda, ostatní komunikace</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1307, 1339, 1340, 1341/1, 1343, 1345, 1346, 1365, 1371</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -1076,47 +1048,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V-76826/2024-101</t>
+          <t>V-2354/2025-509</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2025</v>
       </c>
       <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45779.40665509259</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>45644.67494212963</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="n">
-        <v>2723</v>
+        <v>715</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1125,26 +1097,22 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>OB, SV</t>
-        </is>
-      </c>
+        <v>1750000</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>jiná plocha, zahrada</t>
+          <t>manipulační plocha</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2285/1, 2286</t>
+          <t>458/21</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>2448</t>
         </is>
       </c>
     </row>
@@ -1154,17 +1122,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V-75618/2024-101</t>
+          <t>V-2313/2025-509</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2025</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45642.52130787037</v>
+        <v>45777.45212962963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1175,26 +1143,26 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>196</v>
+        <v>922</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1203,26 +1171,22 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>500000</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>278/1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>542</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1196,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V-75458/2024-101</t>
+          <t>V-2306/2025-509</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2025</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>45642.39537037037</v>
+        <v>45777.41471064815</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1253,26 +1217,26 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>723</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1281,26 +1245,22 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>380000</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>1750000</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>manipulační plocha</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3496/9</t>
+          <t>458/46</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>2420</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1270,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V-75303/2024-101</t>
+          <t>V-1890/2025-509</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2025</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45639.48475694445</v>
+        <v>45756.52206018518</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1331,26 +1291,26 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2872</v>
+        <v>406</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí u Teplic</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633381</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1359,26 +1319,22 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>54955500</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>VN-F</t>
-        </is>
-      </c>
+        <v>1218000</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>zeleň</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1676/65</t>
+          <t>171</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>3000</t>
         </is>
       </c>
     </row>
@@ -1388,47 +1344,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-75240/2024-101</t>
+          <t>V-1799/2025-509</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2025</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45754.47596064815</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>45639.45305555555</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1437,26 +1393,22 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>601612</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>5600</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>21/11, 21/12</t>
+          <t>252/2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1418,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V-69272/2024-101</t>
+          <t>V-1786/2025-509</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45617.5034375</v>
+        <v>45754.38422453704</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1484,29 +1436,29 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>994</v>
+        <v>845</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1515,26 +1467,22 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>OB, OV</t>
-        </is>
-      </c>
+        <v>1990000</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>zeleň</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2845/14, 2855/8</t>
+          <t>274/118</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>2355</t>
         </is>
       </c>
     </row>
@@ -1544,17 +1492,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-67618/2024-101</t>
+          <t>V-887/2025-509</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45610.56474537037</v>
+        <v>45707.64144675926</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1562,29 +1510,29 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1123</v>
+        <v>39</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>732583</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Horní Měcholupy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1593,26 +1541,22 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>OV-F, SP</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>jiná plocha, zahrada</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2747/73, 520/17, 520/48, 520/52</t>
+          <t>255/2, 256/2</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1566,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V-65779/2024-101</t>
+          <t>V-798/2025-509</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45603.57430555556</v>
+        <v>45702.44231481481</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1640,29 +1584,29 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3210</v>
+        <v>897</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>732583</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Horní Měcholupy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1671,26 +1615,22 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>34409856</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>OV-E, OV-F, SP</t>
-        </is>
-      </c>
+        <v>1704300</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>jiná plocha, zeleň</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2747/71, 2747/72, 2747/73, 518/38, 520/20, 520/49, 520/51, 521/381, 521/415, 521/416</t>
+          <t>280/35</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1640,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V-40630/2024-101</t>
+          <t>V-594/2025-509</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45485.38900462963</v>
+        <v>45691.65041666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1718,29 +1658,29 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>1104</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Běhánky</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633411</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1749,26 +1689,22 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>175000</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>PZO</t>
-        </is>
-      </c>
+        <v>800000</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>zastavěná plocha a nádvoří</t>
+          <t>jiná plocha, zahrada</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4031/31</t>
+          <t>611/2, 612</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>725</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1714,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V-36255/2024-101</t>
+          <t>V-458/2025-509</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45464.46828703704</v>
+        <v>45684.48357638889</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1796,29 +1732,29 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>912</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1827,26 +1763,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>1732800</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>zastavěná plocha a nádvoří</t>
+          <t>neplodná půda, trvalý travní porost</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>654/7</t>
+          <t>280/32, 281/9</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1788,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V-35213/2024-101</t>
+          <t>V-365/2025-509</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45461.3869212963</v>
+        <v>45679.43196759259</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1874,29 +1806,29 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>433</v>
+        <v>816</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1905,26 +1837,22 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>SV-D</t>
-        </is>
-      </c>
+        <v>1700000</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>jiná plocha, zahrada</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4174/1, 4174/2, 4174/3, 4174/4, 4174/5</t>
+          <t>274/135</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>2083</t>
         </is>
       </c>
     </row>
@@ -1934,17 +1862,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>V-27182/2024-101</t>
+          <t>V-148/2025-509</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45425.49413194445</v>
+        <v>45670.48196759259</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1955,26 +1883,26 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>906</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>731943</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Strašnice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1983,26 +1911,22 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>200000</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>ZMK</t>
-        </is>
-      </c>
+        <v>1800000</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4501/152</t>
+          <t>274/114</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>1987</t>
         </is>
       </c>
     </row>
@@ -2012,17 +1936,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V-26380/2024-101</t>
+          <t>V-3/2025-509</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45419.41424768518</v>
+        <v>45659.44414351852</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2030,29 +1954,29 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>1092</v>
+        <v>1844</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>732451</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2061,26 +1985,22 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>25300000</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>OP, SV-D</t>
-        </is>
-      </c>
+        <v>3450000</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>neplodná půda, trvalý travní porost</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>890/68, 906/15, 906/16, 908/6, 943/2</t>
+          <t>274/119, 274/120, 281/7</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>1871</t>
         </is>
       </c>
     </row>
@@ -2090,47 +2010,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V-9328/2024-101</t>
+          <t>V-7128/2024-509</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45656.61038194445</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>45338.38943287037</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Smlouva kupní, Smlouva o zániku předkupního práva</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>2791</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>732451</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2139,26 +2059,22 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>176000</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>6343660</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>498/4</t>
+          <t>437/11, 437/12, 437/13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>2273</t>
         </is>
       </c>
     </row>
@@ -2168,17 +2084,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>V-4195/2024-101</t>
+          <t>V-6947/2024-509</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45315.37703703704</v>
+        <v>45642.51956018519</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2189,26 +2105,26 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí-Pozorka</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633461</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2217,26 +2133,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>254037</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>zastavěná plocha a nádvoří</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>654/7</t>
+          <t>309/32</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>1620</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2158,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V-70691/2023-101</t>
+          <t>V-6921/2024-509</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45289.48384259259</v>
+        <v>45642.38092592593</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2264,29 +2176,29 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>309</v>
+        <v>2473</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2295,26 +2207,22 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6675000</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>4728374</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>jiná plocha, orná půda</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>437/20, 437/21, 437/31, 447/64</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>1912</t>
         </is>
       </c>
     </row>
@@ -2324,17 +2232,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>V-70042/2023-101</t>
+          <t>V-6920/2024-509</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45282.50065972222</v>
+        <v>45642.37916666667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,29 +2250,29 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>316</v>
+        <v>2501</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>732451</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Malešice</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2373,26 +2281,22 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>4781912</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>jiná plocha, orná půda</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>80/2</t>
+          <t>437/16, 437/17, 437/32, 447/62</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>1912</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2306,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>V-64568/2023-101</t>
+          <t>V-6889/2024-509</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45260.45768518518</v>
+        <v>45639.37368055555</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2423,26 +2327,26 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2451,26 +2355,22 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>12775000</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>SV-D</t>
-        </is>
-      </c>
+        <v>2476040</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1653/3</t>
+          <t>437/23</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>2390</t>
         </is>
       </c>
     </row>
@@ -2480,17 +2380,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>V-46411/2022-101</t>
+          <t>V-6880/2024-509</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44775.4552662037</v>
+        <v>45638.504375</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2501,26 +2401,26 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>302</v>
+        <v>758</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2529,26 +2429,22 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>OV</t>
-        </is>
-      </c>
+        <v>1750000</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>manipulační plocha</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>524/15</t>
+          <t>458/22</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>2309</t>
         </is>
       </c>
     </row>
@@ -2558,17 +2454,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>V-45270/2022-101</t>
+          <t>V-6823/2024-509</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>44769.5263425926</v>
+        <v>45636.48131944444</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2579,26 +2475,26 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>558</v>
+        <v>863</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Mstišov</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2607,26 +2503,22 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>SV-D</t>
-        </is>
-      </c>
+        <v>2062570</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1302/48</t>
+          <t>437/14</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>2390</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2528,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V-43470/2022-101</t>
+          <t>V-6252/2024-509</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>44761.47697916667</v>
+        <v>45608.5503125</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2654,29 +2546,29 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2685,26 +2577,22 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>150724</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>zahrada, zastavěná plocha a nádvoří</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>386/1, 386/2</t>
+          <t>268/4</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>1492</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2602,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>V-27575/2022-101</t>
+          <t>V-6199/2024-509</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>44683.70978009259</v>
+        <v>45607.39695601852</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2735,26 +2623,26 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>210</v>
+        <v>868</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>732052</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Hostivař</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2763,26 +2651,22 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>OV-C</t>
-        </is>
-      </c>
+        <v>1649200</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>522/4</t>
+          <t>274/115</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -2792,17 +2676,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>V-66483/2020-101</t>
+          <t>V-6118/2024-509</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44141.43905092592</v>
+        <v>45601.55800925926</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2810,29 +2694,29 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>910</v>
+        <v>3197</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2841,26 +2725,22 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>OB-D</t>
-        </is>
-      </c>
+        <v>6074300</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>349/227</t>
+          <t>274/109, 274/111, 274/72</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -2870,17 +2750,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V-21491/2020-101</t>
+          <t>V-6089/2024-509</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>43941.4478125</v>
+        <v>45600.59753472222</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,29 +2768,29 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>522</v>
+        <v>2007</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2919,26 +2799,22 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6680000</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
+        <v>3800000</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>439/52</t>
+          <t>274/116, 274/93</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>1893</t>
         </is>
       </c>
     </row>
@@ -2948,17 +2824,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>V-15586/2020-101</t>
+          <t>V-6058/2024-509</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>43902.48244212963</v>
+        <v>45597.37184027778</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2969,26 +2845,26 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>832</v>
+        <v>1047</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí u Teplic</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633381</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2997,26 +2873,22 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>OB-D</t>
-        </is>
-      </c>
+        <v>705000</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>349/25</t>
+          <t>1025/9</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>673</t>
         </is>
       </c>
     </row>
@@ -3026,17 +2898,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>V-86046/2019-101</t>
+          <t>V-6006/2024-509</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>43829.60714120371</v>
+        <v>45595.39693287037</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3047,26 +2919,26 @@
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>308</v>
+        <v>2118</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Hlavní město Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Drahůnky</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>633429</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Štěrboholy</t>
+          <t>Dubí</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3075,26 +2947,22 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4250000</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
+        <v>4024200</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>trvalý travní porost</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>269, 270</t>
+          <t>280/33, 280/34</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -3104,75 +2972,367 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V-86597/2014-101</t>
+          <t>V-5814/2024-509</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="D35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45586.41773148148</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1019</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>633429</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Dubí</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>trvalý travní porost</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>274/73</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V-5481/2024-509</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45572.3446875</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>41996.50581018518</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="H36" t="n">
+        <v>777</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>633429</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Dubí</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1476300</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>trvalý travní porost</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>274/117</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V-1970/2024-509</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>45392.36751157408</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>202</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>633429</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Dubí</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>trvalý travní porost</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>283/1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>V-205/2024-509</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D38" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>838</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Malešice</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>731943</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Strašnice</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1590/14</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>17900</t>
+      <c r="E38" s="2" t="n">
+        <v>45303.39259259259</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>273</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Běhánky</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>633411</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Dubí</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>205800</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>zahrada</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>288/2</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>V-127/2024-509</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45300.49328703704</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2426</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Drahůnky</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>633429</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Dubí</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>3396400</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>orná půda, trvalý travní porost</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>274/75, 365/24, 365/29</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1400</t>
         </is>
       </c>
     </row>

--- a/VALUO/pozemky_data.xlsx
+++ b/VALUO/pozemky_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,47 +530,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V-7059/2025-210</t>
+          <t>V-32330/2025-101</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45839.38993055555</v>
+        <v>45800.4377662037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zániku věcného břemene, Smlouva o zřízení věcného břemene - bezúplatná</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>600</v>
+        <v>716</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,22 +579,26 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>5800002</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>ostatní komunikace, zahrada</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>168/20</t>
+          <t>1013/3, 2428/21</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9777</t>
         </is>
       </c>
     </row>
@@ -604,17 +608,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V-1543/2025-210</t>
+          <t>V-31029/2025-101</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45700.75864583333</v>
+        <v>45796.46834490741</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,29 +626,29 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1470</v>
+        <v>3071</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -653,22 +657,26 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>24500000</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ZMK</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>manipulační plocha</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>259/100</t>
+          <t>1433/12, 1433/13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>7978</t>
         </is>
       </c>
     </row>
@@ -678,47 +686,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V-13286/2024-210</t>
+          <t>V-25140/2025-101</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2025</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45645.18021990741</v>
+        <v>45770.33414351852</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Usnesení soudního exekutora o udělení příklepu</t>
+          <t>Smlouva kupní</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>1463</v>
+        <v>43241</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -727,22 +735,26 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6511333</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>100000000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>IZ, PS, ZMK</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>orná půda, ovocný sad</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>259/6</t>
+          <t>1481/1, 2352/1, 2352/10, 2352/11, 2352/12, 2352/2, 2352/20, 2352/22, 2352/30, 2352/31, 2352/4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>2313</t>
         </is>
       </c>
     </row>
@@ -752,17 +764,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V-12867/2024-210</t>
+          <t>V-19568/2025-101</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45637.5732175926</v>
+        <v>45744.49373842592</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -770,29 +782,29 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>1438</v>
+        <v>9833</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -801,9 +813,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>54000000</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>DH, IZ</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>orná půda</t>
@@ -811,12 +827,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>259/145</t>
+          <t>2372/31, 2372/34, 2372/35, 2372/36</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>5492</t>
         </is>
       </c>
     </row>
@@ -826,17 +842,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V-10679/2024-210</t>
+          <t>V-17729/2025-101</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45582.53714120371</v>
+        <v>45737.48583333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -844,29 +860,29 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1479</v>
+        <v>944</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -875,9 +891,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>OB-C</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>orná půda</t>
@@ -885,12 +905,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>259/19</t>
+          <t>2354/42, 2354/43</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>1059</t>
         </is>
       </c>
     </row>
@@ -900,17 +920,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V-6109/2024-210</t>
+          <t>V-3056/2025-101</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45457.40417824074</v>
+        <v>45673.57884259259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -921,26 +941,26 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1711</v>
+        <v>1235</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -949,22 +969,26 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>6490000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>171/2</t>
+          <t>2362/77</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>5255</t>
         </is>
       </c>
     </row>
@@ -974,17 +998,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V-4384/2024-210</t>
+          <t>V-950/2025-101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45414.3870949074</v>
+        <v>45664.50819444445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -995,26 +1019,26 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>619</v>
+        <v>2177</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1023,22 +1047,26 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4952000</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>3850000</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PZO</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>ovocný sad</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>142/30</t>
+          <t>1855/1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>1768</t>
         </is>
       </c>
     </row>
@@ -1048,17 +1076,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V-11811/2021-210</t>
+          <t>V-76318/2024-101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>44427.47060185186</v>
+        <v>45644.39130787037</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1066,29 +1094,29 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>1108</v>
+        <v>41858</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1097,22 +1125,26 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6995000</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>54298200</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>IZ, NL/SP, OV, PS/SP, SV, ZMK</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>koryto vodního toku přirozené nebo upravené, orná půda, ostatní komunikace</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>269/101</t>
+          <t>1470/176, 1477/4, 1478/11, 2350/4, 2350/5, 2350/6, 2350/7, 2351/1, 2351/3, 2351/6, 2352/21, 2352/33, 2352/34, 2352/5, 2444</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>1297</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1154,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V-11577/2021-210</t>
+          <t>V-72229/2024-101</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44424.39930555555</v>
+        <v>45629.38246527778</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1143,26 +1175,26 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1488</v>
+        <v>1548</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1171,22 +1203,26 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>12213983</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>OB-C</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>268/20</t>
+          <t>829/3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>7890</t>
         </is>
       </c>
     </row>
@@ -1196,17 +1232,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V-10364/2021-210</t>
+          <t>V-66945/2024-101</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44400.40045138889</v>
+        <v>45609.38230324074</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1217,26 +1253,26 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1334</v>
+        <v>711</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1245,22 +1281,26 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8250000</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>18200000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>268/21</t>
+          <t>2466/4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>25598</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1310,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V-7418/2021-210</t>
+          <t>V-65259/2024-101</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44344.34722222222</v>
+        <v>45602.40625</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1291,26 +1331,26 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1433</v>
+        <v>18909</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1319,9 +1359,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4012400</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>110500000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>OB-A</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>orná půda</t>
@@ -1329,12 +1373,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>259/109</t>
+          <t>2356/2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>5844</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1388,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-5728/2021-210</t>
+          <t>V-57996/2024-101</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>44315.53930555555</v>
+        <v>45569.49055555555</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1362,29 +1406,29 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>964</v>
+        <v>11516</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1393,9 +1437,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1928000</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>17484875</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ZMK, ZMK/SV-B</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>orná půda</t>
@@ -1403,12 +1451,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>259/21</t>
+          <t>2375/6, 2375/7</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1518</t>
         </is>
       </c>
     </row>
@@ -1418,17 +1466,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V-5726/2021-210</t>
+          <t>V-46186/2024-101</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>44315.53679398148</v>
+        <v>45513.46150462963</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1439,26 +1487,26 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>153</v>
+        <v>914</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1467,22 +1515,26 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>244800</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>6000000</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>OV</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ostatní komunikace</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>259/161</t>
+          <t>741</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>6565</t>
         </is>
       </c>
     </row>
@@ -1492,17 +1544,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-927/2021-210</t>
+          <t>V-44601/2024-101</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44221.43571759259</v>
+        <v>45505.5330787037</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1513,26 +1565,26 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1249</v>
+        <v>318</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1541,22 +1593,26 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3350000</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+        <v>7200000</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>259/3</t>
+          <t>1814/5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>22642</t>
         </is>
       </c>
     </row>
@@ -1566,47 +1622,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V-13079/2020-210</t>
+          <t>V-38511/2024-101</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44153.62739583333</v>
+        <v>45475.33479166667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zřízení věcného břemene - úplatná</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>764</v>
+        <v>8382</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1615,22 +1671,26 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
+        <v>148000000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>SV-C</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>282/63</t>
+          <t>2366/17</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>17657</t>
         </is>
       </c>
     </row>
@@ -1640,17 +1700,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V-13034/2020-210</t>
+          <t>V-32174/2024-101</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44153.40392361111</v>
+        <v>45447.36206018519</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1658,29 +1718,29 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1448</v>
+        <v>6461</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1689,9 +1749,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>50000000</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>OB-B, ZMK</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>orná půda</t>
@@ -1699,12 +1763,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>259/150</t>
+          <t>2349/15, 2349/47</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>7739</t>
         </is>
       </c>
     </row>
@@ -1714,17 +1778,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V-11911/2020-210</t>
+          <t>V-24467/2024-101</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44125.62828703703</v>
+        <v>45408.49657407407</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1732,29 +1796,29 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>900</v>
+        <v>923</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1763,22 +1827,26 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6549847</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
+        <v>26300000</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>OB-B</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>jiná plocha, zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>142/26, 653</t>
+          <t>2349/63</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>28494</t>
         </is>
       </c>
     </row>
@@ -1788,17 +1856,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V-11835/2020-210</t>
+          <t>V-24071/2024-101</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44125.3630324074</v>
+        <v>45407.48519675926</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1809,26 +1877,26 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1018</v>
+        <v>1041</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1837,22 +1905,26 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3650000</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
+        <v>24500000</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>259/149</t>
+          <t>561</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>23535</t>
         </is>
       </c>
     </row>
@@ -1862,17 +1934,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>V-5567/2020-210</t>
+          <t>V-24009/2024-101</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43979.34722222222</v>
+        <v>45407.41380787037</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1883,26 +1955,26 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1448</v>
+        <v>914</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Praha-západ</t>
+          <t>Hlavní město Praha</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>669971</t>
+          <t>728314</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Kosoř</t>
+          <t>Kunratice</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1911,22 +1983,1742 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3450000</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>6800000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>OV</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>zahrada</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>7440</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V-20893/2024-101</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45393.51142361111</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>6490000</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>orná půda</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>259/20</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2383</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2362/77</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>5255</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V-16485/2024-101</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45372.49778935185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>313</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>3772894</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SV-E</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>zahrada, zastavěná plocha a nádvoří</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1479, 1480</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12054</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-345/2024-101</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45294.63649305556</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>986</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>8929970</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>OB-C, ZMK</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>jiná plocha</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2420/5, 2420/6, 825/1, 826/4</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>9057</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V-47590/2023-101</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45177.4828587963</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>41</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>115000</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ZMK</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>trvalý travní porost</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2110/38</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V-42230/2023-101</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45147.62395833333</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6210</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ZMK</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>manipulační plocha</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1433/10, 1433/11, 1433/12, 1433/13</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V-38642/2023-101</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45128.3612037037</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3794</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>22531700</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>VN-D</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>orná půda</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2368/29, 2370/11</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V-36815/2023-101</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45118.99244212963</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ZMK</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>jiná plocha, zahrada</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1158, 1159</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>V-33955/2023-101</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45103.44829861111</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Smlouva kupní, Smlouva o zániku předkupního práva</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2430</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SV-C</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>orná půda</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1888/1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V-30332/2023-101</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45084.58635416667</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1454</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>3650000</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>PZO</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ovocný sad, zahrada</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1855/2, 1857/2</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2510</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V-20764/2023-101</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45035.44001157407</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>27550000</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>OB-C</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>orná půda</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2364/24</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>V-20012/2023-101</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45033.37351851852</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1736</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>zahrada</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1866/2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>V-12154/2023-101</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>44991.54622685185</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>403</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SV-C</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>zahrada</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>367/9</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>37221</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>V-9763/2023-101</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>44979.38125</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>550</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>6117000</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>zeleň</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>11122</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>V-1609/2023-101</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>44936.55086805556</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10203</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>OP/NL</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>orná půda</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2357/44</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>V-74539/2022-101</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>44924.39818287037</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>709</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>13912170</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>zastavěná plocha a nádvoří</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2378/54</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>19622</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V-74536/2022-101</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>44924.39534722222</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>909</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>17471641</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>zastavěná plocha a nádvoří</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2378/55</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>19221</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V-40757/2022-101</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>44743.44791666666</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1548</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>12152500</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>OB-C</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>jiná plocha</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>829/3</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>V-39172/2022-101</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>44736.40520833333</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1871</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>OB-C</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>orná půda</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2356/236</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>V-39086/2022-101</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>44736.33447916667</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>257</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1429500</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>zeleň</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>5562</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>V-39047/2022-101</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>44735.54371527778</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>14842</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>30400000</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PS, SV-C, ZMK</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>jiná plocha, orná půda, ovocný sad</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1871, 1872, 2366/34</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V-38307/2022-101</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>44733.42373842592</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>193</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2148000</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>zeleň</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>11130</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>V-36599/2022-101</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>44725.55576388889</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>257</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>728314</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Kunratice</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>parcela</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1429500</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>zeleň</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>5562</t>
         </is>
       </c>
     </row>

--- a/VALUO/pozemky_data.xlsx
+++ b/VALUO/pozemky_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,28 +530,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V-32330/2025-101</t>
+          <t>V-37391/2025-101</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45800.4377662037</v>
+        <v>45820.48770833333</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smlouva kupní, Smlouva o zániku věcného břemene, Smlouva o zřízení věcného břemene - bezúplatná</t>
+          <t>Smlouva kupní</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>716</v>
+        <v>468</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -560,17 +560,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7000000</v>
+        <v>13572000</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -588,17 +588,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ostatní komunikace, zahrada</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1013/3, 2428/21</t>
+          <t>876/3</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>29000</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V-31029/2025-101</t>
+          <t>V-32330/2025-101</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -618,18 +618,18 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45796.46834490741</v>
+        <v>45800.4377662037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zániku věcného břemene, Smlouva o zřízení věcného břemene - bezúplatná</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3071</v>
+        <v>716</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -657,26 +657,26 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24500000</v>
+        <v>7000000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>manipulační plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1433/12, 1433/13</t>
+          <t>1013/3</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9777</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V-25140/2025-101</t>
+          <t>V-30966/2025-101</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2025</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45770.33414351852</v>
+        <v>45796.51835648148</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>43241</v>
+        <v>599</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -716,17 +716,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>727598</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -735,26 +735,26 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>100000000</v>
+        <v>16600000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>IZ, PS, ZMK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>orná půda, ovocný sad</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1481/1, 2352/1, 2352/10, 2352/11, 2352/12, 2352/2, 2352/20, 2352/22, 2352/30, 2352/31, 2352/4</t>
+          <t>528</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>27713</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V-19568/2025-101</t>
+          <t>V-29332/2025-101</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45744.49373842592</v>
+        <v>45789.48586805556</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>9833</v>
+        <v>470</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -794,17 +794,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>54000000</v>
+        <v>11500000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>DH, IZ</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2372/31, 2372/34, 2372/35, 2372/36</t>
+          <t>4635/833</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>24468</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V-17729/2025-101</t>
+          <t>V-8672/2025-101</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45737.48583333333</v>
+        <v>45699.42623842593</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>944</v>
+        <v>818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -872,17 +872,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1000000</v>
+        <v>16000000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -900,17 +900,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2354/42, 2354/43</t>
+          <t>4635/823</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>19560</t>
         </is>
       </c>
     </row>
@@ -920,28 +920,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V-3056/2025-101</t>
+          <t>V-78022/2024-101</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2025</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45649.56675925926</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>45673.57884259259</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" t="n">
-        <v>1235</v>
+        <v>657</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -950,17 +950,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -969,26 +969,26 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6490000</v>
+        <v>20000000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2362/77</t>
+          <t>374/1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>30441</t>
         </is>
       </c>
     </row>
@@ -998,17 +998,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V-950/2025-101</t>
+          <t>V-72229/2024-101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45664.50819444445</v>
+        <v>45629.38246527778</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2177</v>
+        <v>1548</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1047,26 +1047,26 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3850000</v>
+        <v>12213983</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PZO</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ovocný sad</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1855/1</t>
+          <t>829/3</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>7890</t>
         </is>
       </c>
     </row>
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V-76318/2024-101</t>
+          <t>V-71942/2024-101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45628.55680555556</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>45644.39130787037</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
       <c r="H9" t="n">
-        <v>41858</v>
+        <v>1455</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1125,26 +1125,26 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>54298200</v>
+        <v>19350000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>IZ, NL/SP, OV, PS/SP, SV, ZMK</t>
+          <t>VV</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>koryto vodního toku přirozené nebo upravené, orná půda, ostatní komunikace</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1470/176, 1477/4, 1478/11, 2350/4, 2350/5, 2350/6, 2350/7, 2351/1, 2351/3, 2351/6, 2352/21, 2352/33, 2352/34, 2352/5, 2444</t>
+          <t>1652/1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>13299</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V-72229/2024-101</t>
+          <t>V-67753/2024-101</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1164,7 +1164,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45629.38246527778</v>
+        <v>45611.41946759259</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1548</v>
+        <v>724</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>727598</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1203,26 +1203,26 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>12213983</v>
+        <v>4900000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>OB-C</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>jiná plocha</t>
+          <t>zeleň</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>829/3</t>
+          <t>2869/379</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>6768</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-57996/2024-101</t>
+          <t>V-55791/2024-101</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1398,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45569.49055555555</v>
+        <v>45560.64756944445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>11516</v>
+        <v>682</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1437,26 +1437,26 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>17484875</v>
+        <v>9600000</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ZMK, ZMK/SV-B</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2375/6, 2375/7</t>
+          <t>1337/1</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>14076</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V-46186/2024-101</t>
+          <t>V-44601/2024-101</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2024</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45513.46150462963</v>
+        <v>45505.5330787037</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>914</v>
+        <v>318</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6000000</v>
+        <v>7200000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>OV</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1814/5</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>22642</t>
         </is>
       </c>
     </row>
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-44601/2024-101</t>
+          <t>V-39063/2024-101</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2024</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45505.5330787037</v>
+        <v>45476.62331018518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>318</v>
+        <v>727</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1574,17 +1574,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7200000</v>
+        <v>15000000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1814/5</t>
+          <t>3607/2</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>20633</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V-32174/2024-101</t>
+          <t>V-34591/2024-101</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2024</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45447.36206018519</v>
+        <v>45457.33944444444</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>6461</v>
+        <v>809</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1749,26 +1749,26 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>50000000</v>
+        <v>12300000</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>OB-B, ZMK</t>
+          <t>OB-B</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2349/15, 2349/47</t>
+          <t>2466/13</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>15204</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V-24467/2024-101</t>
+          <t>V-32174/2024-101</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2024</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45408.49657407407</v>
+        <v>45447.36206018519</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>923</v>
+        <v>6461</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>26300000</v>
+        <v>50000000</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2349/63</t>
+          <t>2349/47</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>7739</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V-24071/2024-101</t>
+          <t>V-30430/2024-101</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2024</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45407.48519675926</v>
+        <v>45439.60282407407</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1041</v>
+        <v>702</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>24500000</v>
+        <v>12000000</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1651/6</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>17094</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>V-24009/2024-101</t>
+          <t>V-24467/2024-101</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1944,7 +1944,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45407.41380787037</v>
+        <v>45408.49657407407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1983,26 +1983,26 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>6800000</v>
+        <v>26300000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>OV</t>
+          <t>OB-B</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>2349/63</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>28494</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V-20893/2024-101</t>
+          <t>V-24071/2024-101</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2022,7 +2022,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45393.51142361111</v>
+        <v>45407.48519675926</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1235</v>
+        <v>1041</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2061,26 +2061,26 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6490000</v>
+        <v>24500000</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2362/77</t>
+          <t>561</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>23535</t>
         </is>
       </c>
     </row>
@@ -2090,17 +2090,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V-16485/2024-101</t>
+          <t>V-24009/2024-101</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2024</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45372.49778935185</v>
+        <v>45407.41380787037</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>313</v>
+        <v>914</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2139,26 +2139,26 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3772894</v>
+        <v>6800000</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>SV-E</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>zahrada, zastavěná plocha a nádvoří</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1479, 1480</t>
+          <t>741</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7440</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>OB-C, ZMK</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2420/5, 2420/6, 825/1, 826/4</t>
+          <t>825/1</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V-47590/2023-101</t>
+          <t>V-57807/2023-101</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2023</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45177.4828587963</v>
+        <v>45231.39039351852</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>41</v>
+        <v>7547</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>728616</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Modřany</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2295,26 +2295,26 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>115000</v>
+        <v>54570000</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>trvalý travní porost</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2110/38</t>
+          <t>112/1</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>7231</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>V-42230/2023-101</t>
+          <t>V-45061/2023-101</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2334,7 +2334,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45147.62395833333</v>
+        <v>45163.48635416666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6210</v>
+        <v>957</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>727598</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2373,26 +2373,26 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>43000000</v>
+        <v>5685000</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>VV</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>manipulační plocha</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1433/10, 1433/11, 1433/12, 1433/13</t>
+          <t>2583/1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>5940</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>V-38642/2023-101</t>
+          <t>V-40494/2023-101</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2412,7 +2412,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45128.3612037037</v>
+        <v>45139.53332175926</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>3794</v>
+        <v>519</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>727598</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2451,26 +2451,26 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>22531700</v>
+        <v>12000000</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>VN-D</t>
+          <t>VV</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2368/29, 2370/11</t>
+          <t>2869/428</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>23121</t>
         </is>
       </c>
     </row>
@@ -2480,28 +2480,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>V-36815/2023-101</t>
+          <t>V-33955/2023-101</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2023</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45118.99244212963</v>
+        <v>45103.44829861111</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smlouva kupní</t>
+          <t>Smlouva kupní, Smlouva o zániku předkupního práva</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2104</v>
+        <v>2430</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2529,26 +2529,26 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>5700000</v>
+        <v>15000000</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>ZMK</t>
+          <t>SV-C</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>jiná plocha, zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1158, 1159</t>
+          <t>1888/1</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>6173</t>
         </is>
       </c>
     </row>
@@ -2558,28 +2558,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>V-33955/2023-101</t>
+          <t>V-22684/2023-101</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2023</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45103.44829861111</v>
+        <v>45043.54092592592</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smlouva kupní, Smlouva o zániku předkupního práva</t>
+          <t>Smlouva kupní</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>2430</v>
+        <v>2185</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>727598</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kunratice</t>
+          <t>Krč</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2607,26 +2607,26 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>15000000</v>
+        <v>15949022</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>SV-C</t>
+          <t>SV-I</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1888/1</t>
+          <t>2/7, 3320/15, 3320/16</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>7299</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2636,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V-30332/2023-101</t>
+          <t>V-20764/2023-101</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2023</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45084.58635416667</v>
+        <v>45035.44001157407</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3650000</v>
+        <v>27550000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PZO</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ovocný sad, zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1855/2, 1857/2</t>
+          <t>2364/24</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>19000</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>V-20764/2023-101</t>
+          <t>V-20012/2023-101</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2023</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45035.44001157407</v>
+        <v>45033.37351851852</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1450</v>
+        <v>1736</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2763,26 +2763,26 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>27550000</v>
+        <v>18000000</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>OB-C</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>orná půda</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2364/24</t>
+          <t>1866/2</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>10369</t>
         </is>
       </c>
     </row>
@@ -2792,17 +2792,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>V-20012/2023-101</t>
+          <t>V-9763/2023-101</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2023</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45033.37351851852</v>
+        <v>44979.38125</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1736</v>
+        <v>550</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>18000000</v>
+        <v>6117000</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2850,17 +2850,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>zeleň</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1866/2</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11122</t>
         </is>
       </c>
     </row>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V-12154/2023-101</t>
+          <t>V-39172/2022-101</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44991.54622685185</v>
+        <v>44736.40520833333</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>403</v>
+        <v>1871</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2919,26 +2919,26 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>SV-C</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>orná půda</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>367/9</t>
+          <t>2356/236</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>6414</t>
         </is>
       </c>
     </row>
@@ -2948,28 +2948,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>V-9763/2023-101</t>
+          <t>V-95999/2021-101</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>44550.65252314815</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>44979.38125</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
       <c r="H33" t="n">
-        <v>550</v>
+        <v>1063</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2997,26 +2997,26 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6117000</v>
+        <v>15800000</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OB-B, OB-C</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>zeleň</t>
+          <t>ostatní komunikace, zahrada</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>999/5, 999/7</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>14864</t>
         </is>
       </c>
     </row>
@@ -3026,28 +3026,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>V-1609/2023-101</t>
+          <t>V-58344/2020-101</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>44109.56383101852</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Smlouva kupní</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>44936.55086805556</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
       <c r="H34" t="n">
-        <v>10203</v>
+        <v>1705</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3075,11 +3075,11 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>12000000</v>
+        <v>25575000</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>OP/NL</t>
+          <t>OB-C</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2357/44</t>
+          <t>2354/56, 2354/57</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>15000</t>
         </is>
       </c>
     </row>
@@ -3104,17 +3104,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V-74539/2022-101</t>
+          <t>V-24941/2020-101</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44924.39818287037</v>
+        <v>43957.48010416667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>709</v>
+        <v>891</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3153,572 +3153,26 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>13912170</v>
+        <v>9500000</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>zastavěná plocha a nádvoří</t>
+          <t>zahrada</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2378/54</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>19622</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>V-74536/2022-101</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>44924.39534722222</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>909</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>17471641</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>zastavěná plocha a nádvoří</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2378/55</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>19221</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>V-40757/2022-101</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D37" t="n">
-        <v>7</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>44743.44791666666</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1548</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>12152500</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>OB-C</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>jiná plocha</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>829/3</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7850</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>V-39172/2022-101</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D38" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>44736.40520833333</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1871</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>OB-C</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>orná půda</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2356/236</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>V-39086/2022-101</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>44736.33447916667</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>257</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1429500</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>zeleň</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>10/14</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>5562</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>V-39047/2022-101</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>44735.54371527778</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>14842</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>30400000</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>PS, SV-C, ZMK</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>jiná plocha, orná půda, ovocný sad</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1871, 1872, 2366/34</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>V-38307/2022-101</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>44733.42373842592</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>193</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>2148000</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>zeleň</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>10/15</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>11130</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>V-36599/2022-101</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>44725.55576388889</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Smlouva kupní</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>257</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>728314</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Kunratice</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>parcela</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>1429500</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>zeleň</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>10/14</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>5562</t>
+          <t>10662</t>
         </is>
       </c>
     </row>
